--- a/erp-server/erp-server-mrp/src/main/resources/excel/purchaseSuggestion.xlsx
+++ b/erp-server/erp-server-mrp/src/main/resources/excel/purchaseSuggestion.xlsx
@@ -1103,7 +1103,7 @@
     <col min="17" max="17" width="15.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:17">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
